--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009726</v>
+        <v>0.00942</v>
       </c>
       <c r="C3" t="n">
-        <v>0.316828</v>
+        <v>0.306859</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009596</v>
+        <v>0.009316</v>
       </c>
       <c r="C4" t="n">
-        <v>0.986716</v>
+        <v>0.988984</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00942</v>
+        <v>0.009438</v>
       </c>
       <c r="C3" t="n">
-        <v>0.306859</v>
+        <v>0.307464</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009316</v>
+        <v>0.009338000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.988984</v>
+        <v>0.989362</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009438</v>
+        <v>0.010163</v>
       </c>
       <c r="C3" t="n">
-        <v>0.307464</v>
+        <v>0.331086</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009338000000000001</v>
+        <v>0.010026</v>
       </c>
       <c r="C4" t="n">
-        <v>0.989362</v>
+        <v>0.9865159999999999</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.010163</v>
+        <v>0.010048</v>
       </c>
       <c r="C3" t="n">
-        <v>0.331086</v>
+        <v>0.327336</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.010026</v>
+        <v>0.009904</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9865159999999999</v>
+        <v>0.985641</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.010048</v>
+        <v>0.009207999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.327336</v>
+        <v>0.299965</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009904</v>
+        <v>0.00907</v>
       </c>
       <c r="C4" t="n">
-        <v>0.985641</v>
+        <v>0.985035</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.030697</v>
+        <v>0.018847</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009207999999999999</v>
+        <v>0.004788</v>
       </c>
       <c r="C3" t="n">
-        <v>0.299965</v>
+        <v>0.254066</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00907</v>
+        <v>0.004867</v>
       </c>
       <c r="C4" t="n">
-        <v>0.985035</v>
+        <v>1.016448</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004788</v>
+        <v>0.004856</v>
       </c>
       <c r="C3" t="n">
-        <v>0.254066</v>
+        <v>0.257659</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004867</v>
+        <v>0.004934</v>
       </c>
       <c r="C4" t="n">
-        <v>1.016448</v>
+        <v>1.015962</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004856</v>
+        <v>0.004526</v>
       </c>
       <c r="C3" t="n">
-        <v>0.257659</v>
+        <v>0.240135</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004934</v>
+        <v>0.004526</v>
       </c>
       <c r="C4" t="n">
-        <v>1.015962</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004526</v>
+        <v>0.004444</v>
       </c>
       <c r="C3" t="n">
-        <v>0.240135</v>
+        <v>0.235812</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004526</v>
+        <v>0.004444</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004444</v>
+        <v>0.004705</v>
       </c>
       <c r="C3" t="n">
-        <v>0.235812</v>
+        <v>0.249664</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004444</v>
+        <v>0.004705</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004705</v>
+        <v>0.004757</v>
       </c>
       <c r="C3" t="n">
-        <v>0.249664</v>
+        <v>0.252407</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004705</v>
+        <v>0.004757</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004757</v>
+        <v>0.004786</v>
       </c>
       <c r="C3" t="n">
-        <v>0.252407</v>
+        <v>0.253959</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004757</v>
+        <v>0.004786</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004786</v>
+        <v>0.005211</v>
       </c>
       <c r="C3" t="n">
-        <v>0.253959</v>
+        <v>0.276488</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004786</v>
+        <v>0.005211</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005211</v>
+        <v>0.005219</v>
       </c>
       <c r="C3" t="n">
-        <v>0.276488</v>
+        <v>0.276896</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005211</v>
+        <v>0.005219</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005219</v>
+        <v>0.0053</v>
       </c>
       <c r="C3" t="n">
-        <v>0.276896</v>
+        <v>0.281224</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005219</v>
+        <v>0.0053</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0053</v>
+        <v>0.005309</v>
       </c>
       <c r="C3" t="n">
-        <v>0.281224</v>
+        <v>0.281677</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0053</v>
+        <v>0.005309</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005309</v>
+        <v>0.005583</v>
       </c>
       <c r="C3" t="n">
-        <v>0.281677</v>
+        <v>0.296211</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005309</v>
+        <v>0.005583</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
